--- a/output/pdf_financials_xlsx/CYM.xlsx
+++ b/output/pdf_financials_xlsx/CYM.xlsx
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>2.613884</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>2.812646</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>2.779248</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>2.613884</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>2.812646</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>2.779248</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1.006497</v>
+        <v>-1.607387</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.8366209999999999</v>
+        <v>-1.976025</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-4.082431</v>
@@ -977,22 +977,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.028031</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003082</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002576</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.036134</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.047747</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.0006089999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
@@ -1894,22 +1894,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.605534</v>
+        <v>-4.577503</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.141272</v>
+        <v>-5.13819</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.051908</v>
+        <v>-4.054484</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.785014</v>
+        <v>-4.821148</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.44344</v>
+        <v>0.395693</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.824381</v>
+        <v>-1.82499</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-1.171207</v>
@@ -1924,7 +1924,7 @@
         <v>-1.116178</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.359403</v>
+        <v>-1.359478</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2002,22 +2002,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.984854</v>
+        <v>-2.956823</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.566695</v>
+        <v>-3.563613</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.466667</v>
+        <v>-2.469243</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.214683</v>
+        <v>-3.250817</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.562591</v>
+        <v>0.514844</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.735133</v>
+        <v>-1.735742</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-1.104759</v>
@@ -2032,7 +2032,7 @@
         <v>-1.055797</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.297744</v>
+        <v>-1.297819</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2057,22 +2057,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-296.5586583963986</v>
+        <v>-293.773652579193</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-426.3214765108693</v>
+        <v>-425.9530898698455</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-133.1439271263802</v>
+        <v>-133.2829725493244</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-114.9972240545688</v>
+        <v>-116.2898273047144</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>60.78680518414073</v>
+        <v>55.62783963523012</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-219.9982756500229</v>
+        <v>-220.0754910276745</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>-68.65609774286567</v>
@@ -2087,7 +2087,7 @@
         <v>-34.65671276304858</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-49.09181147446722</v>
+        <v>-49.09464861789504</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E235" s="5" t="n">
@@ -35374,7 +35374,11 @@
           <t>Selling, general and administrative costs</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E316" s="5" t="n">
         <v>2.613884</v>
       </c>
@@ -35544,7 +35548,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E318" s="5" t="n">
